--- a/results/data_quality_report/data_cleaning_tracking.xlsx
+++ b/results/data_quality_report/data_cleaning_tracking.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -580,6 +580,24 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6 · Remove outlier Price (IQR ×1.5)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>31021</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5143</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Price ngoài [-21,750, 45,050] triệu — fit từ train</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
